--- a/src/classifications/cde_add.xlsx
+++ b/src/classifications/cde_add.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wavicledata-my.sharepoint.com/personal/rajesh_puchakayala_wavicledata_com/Documents/Desktop/project/perview/src/classifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FAA22FC-9400-42E8-AF4B-6202CEBD0975}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3F0D337-1A90-4061-B20B-50AB57AFA0AD}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SQL Server" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
   <si>
     <t>column_name</t>
   </si>
@@ -33,17 +33,20 @@
     <t>classification</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>credit_card_number</t>
+  </si>
+  <si>
+    <t>MICROSOFT.GOVERNMENT.AUSTRIA.IDENTITY.CARD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,6 +68,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color rgb="FF242424"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -110,13 +119,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -132,10 +142,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -426,7 +432,7 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="1" max="1" width="45.28515625" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
@@ -438,14 +444,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -472,10 +473,10 @@
     </row>
     <row r="2" spans="1:2" ht="17.850000000000001" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -529,10 +530,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="1" max="1" width="49.42578125" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
@@ -542,6 +543,14 @@
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="29.95" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/src/classifications/cde_add.xlsx
+++ b/src/classifications/cde_add.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wavicledata-my.sharepoint.com/personal/rajesh_puchakayala_wavicledata_com/Documents/Desktop/project/perview/src/classifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3F0D337-1A90-4061-B20B-50AB57AFA0AD}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0321B58-CB57-4B65-9FEF-6F523DB06953}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
   <si>
     <t>column_name</t>
   </si>
@@ -36,17 +36,23 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>credit_card_number</t>
+    <t>MICROSOFT.PERSONAL.NAME</t>
   </si>
   <si>
-    <t>MICROSOFT.GOVERNMENT.AUSTRIA.IDENTITY.CARD</t>
+    <t>aadhaar_number</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>address</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,6 +74,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color rgb="FF242424"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -119,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -127,6 +139,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -142,6 +155,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,7 +547,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.42578125" customWidth="1"/>
@@ -547,10 +564,26 @@
     </row>
     <row r="2" spans="1:2" ht="29.95" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
+    </row>
+    <row r="3" spans="1:2" ht="29.95" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29.95" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
